--- a/data/memories/memory_01/locales/es/documents/hr/Employee Registry v2.xlsx
+++ b/data/memories/memory_01/locales/es/documents/hr/Employee Registry v2.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Employee Registry Version 2</t>
+          <t>Registro de Empleados Versión 2</t>
         </is>
       </c>
     </row>
@@ -445,7 +445,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Interno</t>
         </is>
       </c>
     </row>
@@ -469,55 +469,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Recursos humanos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Updated Employee Registry</t>
+          <t>Registro de empleados actualizado</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>This version replaces the previous employee registry after the organisational restructuring process. Several fields have been updated to reflect current departmental assignments.</t>
+          <t>Esta versión reemplaza el registro de empleados anterior luego del proceso de reestructuración organizacional. Se han actualizado varios campos para reflejar las asignaciones departamentales actuales.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Current Records</t>
+          <t>Registros actuales</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IDENTIFICACIÓN</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Empleado</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Posición</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Verificación</t>
         </is>
       </c>
     </row>
@@ -529,22 +529,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sarah K.</t>
+          <t>sara k.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Gestión</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Gerente de Operaciones</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verificado</t>
         </is>
       </c>
     </row>
@@ -561,17 +561,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finanzas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Financial Analyst</t>
+          <t>Analista financiero</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verificado</t>
         </is>
       </c>
     </row>
@@ -583,22 +583,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Laura L.</t>
+          <t>laura l.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Recursos humanos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HR Specialist</t>
+          <t>Especialista en Recursos Humanos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verificado</t>
         </is>
       </c>
     </row>
@@ -610,22 +610,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Oliver M.</t>
+          <t>óliver m.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Instalaciones</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Facilities Coordinator</t>
+          <t>Coordinador de Instalaciones</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verificado</t>
         </is>
       </c>
     </row>
@@ -642,17 +642,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ÉL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Administrador de sistemas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verificado</t>
         </is>
       </c>
     </row>
@@ -664,153 +664,153 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M. R.</t>
+          <t>SEÑOR.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Not Assigned</t>
+          <t>No asignado</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Requires Review</t>
+          <t>Requiere revisión</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Changes From Previous Version</t>
+          <t>Cambios de la versión anterior</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Campo</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Previous</t>
+          <t>Anterior</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Actual</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Department Structure</t>
+          <t>Estructura del departamento</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Previous Organisation</t>
+          <t>Organización anterior</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New Organisation</t>
+          <t>Nueva organización</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Document References</t>
+          <t>Referencias de documentos</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Mezclado</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EMP-006 Assignment</t>
+          <t>Asignación EMP-006</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Operations Coordinator</t>
+          <t>Coordinador de Operaciones</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Not Assigned</t>
+          <t>No asignado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HR Notes</t>
+          <t>Notas de recursos humanos</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>The EMP-006 record remains active in historical documentation but cannot currently be assigned to a department using available records.</t>
+          <t>El registro EMP-006 permanece activo en la documentación histórica, pero actualmente no se puede asignar a un departamento utilizando los registros disponibles.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Previous documentation references this employee in relation to operational projects and management meetings. Supporting records should be reviewed before any modification is made.</t>
+          <t>La documentación anterior hace referencia a este empleado en relación con proyectos operativos y reuniones de gestión. Los registros de respaldo deben revisarse antes de realizar cualquier modificación.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Approval Status</t>
+          <t>Estado de aprobación</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>• Management review completed.</t>
+          <t>• Revisión de la gestión completada.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>• HR approval pending.</t>
+          <t>• Aprobación de RRHH pendiente.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>• Archive references retained.</t>
+          <t>• Se conservan las referencias de archivo.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>• Previous registry preserved.</t>
+          <t>• Se conserva el registro anterior.</t>
         </is>
       </c>
     </row>
